--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129747829</v>
       </c>
       <c r="B2" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129746803</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129747829</v>
       </c>
       <c r="B2" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129746803</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129747808</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Uttertjärnskojan, Uttertjärnskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478631</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6841327</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129747829</v>
       </c>
       <c r="B2" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129746803</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129747808</v>
       </c>
       <c r="B4" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129747829</v>
       </c>
       <c r="B2" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129746803</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129747808</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129747829</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129746803</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129747808</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129747829</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129746803</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129747808</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129747829</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,11 +775,11 @@
         <v>129746803</v>
       </c>
       <c r="B3" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -872,7 +872,7 @@
         <v>129747808</v>
       </c>
       <c r="B4" t="n">
-        <v>80200</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,6 +963,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129747722</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Uttertjärnskojan, Uttertjärnskojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478649</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6841376</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50654-2025 artfynd.xlsx
+++ b/artfynd/A 50654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129747829</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129746803</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129747808</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129747722</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>